--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
@@ -6680,7 +6680,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260805_205716.xlsx
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
